--- a/output/pdf_financials_xlsx/ILI.xlsx
+++ b/output/pdf_financials_xlsx/ILI.xlsx
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.319571</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.319571</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.319571</v>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.319571</v>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.319571</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2909,16 +2909,16 @@
         <v>0.020638</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.043033</v>
+        <v>0.013951</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.051306</v>
+        <v>0.018934</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.182815</v>
+        <v>0.046235</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.296867</v>
+        <v>0.121009</v>
       </c>
     </row>
     <row r="49">
@@ -5199,46 +5199,46 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.272174</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.053198</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.21702</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.413194</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.947325</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.002725</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.094479</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.300586</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.943088</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.203688</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.582988</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.304086</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.746663</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.746663</v>
       </c>
     </row>
     <row r="93">
@@ -6492,43 +6492,43 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.438245</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.193621</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>0.308268</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>3.122429</v>
+        <v>2.987737</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.747098</v>
+        <v>0.57619</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.294305</v>
+        <v>0.172438</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.701483</v>
+        <v>0.657236</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.6389089999999999</v>
+        <v>-2.279211</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.430563</v>
+        <v>0.191071</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.5946939999999999</v>
+        <v>-0.339493</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>1.21682</v>
+        <v>-0.340105</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3.531399</v>
+        <v>-0.393502</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-5.872586</v>
       </c>
     </row>
     <row r="119">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8358,7 +8358,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -8756,7 +8760,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9686,7 +9690,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -10032,7 +10040,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11498,7 +11510,11 @@
           <t>Share-based payment reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12428,7 +12444,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
         <v>3.272174</v>
       </c>
@@ -13652,7 +13672,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -22300,7 +22324,11 @@
           <t>Write-off of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -23588,7 +23616,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -47905,10 +47937,10 @@
         </is>
       </c>
       <c r="F476" s="5" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="G476" s="5" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="H476" t="inlineStr">
         <is>
@@ -48077,10 +48109,10 @@
         </is>
       </c>
       <c r="F478" s="5" t="n">
-        <v>0.356075</v>
+        <v>-0.356075</v>
       </c>
       <c r="G478" s="5" t="n">
-        <v>1.343984</v>
+        <v>-1.343984</v>
       </c>
       <c r="H478" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ILI.xlsx
+++ b/output/pdf_financials_xlsx/ILI.xlsx
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-1.9e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003452</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1017,10 +1017,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.077496</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.07427599999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.337075</v>
+        <v>-0.337056</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.333984</v>
+        <v>-1.330532</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.319571</v>
@@ -1866,10 +1866,10 @@
         <v>-0.497873</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.637366</v>
+        <v>0.55987</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.269126</v>
+        <v>0.19485</v>
       </c>
     </row>
     <row r="28">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.337075</v>
+        <v>-0.337056</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.333984</v>
+        <v>-1.330532</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.319571</v>
@@ -1968,10 +1968,10 @@
         <v>-0.497873</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.637366</v>
+        <v>0.55987</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.269126</v>
+        <v>0.19485</v>
       </c>
     </row>
     <row r="30">
@@ -2205,16 +2205,16 @@
         <v>0.017245</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001874</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000575</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000285</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.067299</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.286758</v>
@@ -2303,16 +2303,16 @@
         <v>0.017245</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.003917</v>
+        <v>0.005791</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.001393</v>
+        <v>0.001968</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.000348</v>
+        <v>0.000633</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.273648</v>
+        <v>0.340947</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.346258</v>
@@ -2894,13 +2894,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.005218</v>
+        <v>0.004643</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.007599</v>
+        <v>0.007314</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.080161</v>
+        <v>0.012862</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.109738</v>
@@ -2909,16 +2909,16 @@
         <v>0.020638</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.013951</v>
+        <v>0.043033</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.018934</v>
+        <v>0.051306</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.046235</v>
+        <v>0.182815</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.121009</v>
+        <v>0.296867</v>
       </c>
     </row>
     <row r="49">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -28650,7 +28650,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -45524,7 +45524,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -47670,7 +47670,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
